--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/7mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/7mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.64040379629</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>827.3011712675581</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>814.1382240427224</v>
+        <v>0.249550032</v>
+      </c>
+      <c r="Y2">
+        <v>0.262400512</v>
+      </c>
+      <c r="Z2">
+        <v>0.362117725565959</v>
+      </c>
+      <c r="AA2">
+        <v>6.425240000000002</v>
+      </c>
+      <c r="AB2">
+        <v>0.05723893086077873</v>
+      </c>
+      <c r="AC2">
+        <v>47.35383454322502</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.64051953704</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>817.7694297549128</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>817.3195818614976</v>
+      </c>
+      <c r="X3">
+        <v>0.249550986</v>
+      </c>
+      <c r="Y3">
+        <v>0.262382686</v>
+      </c>
+      <c r="Z3">
+        <v>0.3621054660263316</v>
+      </c>
+      <c r="AA3">
+        <v>6.415850000000006</v>
+      </c>
+      <c r="AB3">
+        <v>0.05731826699504491</v>
+      </c>
+      <c r="AC3">
+        <v>46.87312651507772</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.64063585648</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>818.4025367761526</v>
       </c>
-      <c r="V4">
-        <v>5.329800130334091</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.249554798</v>
+      </c>
+      <c r="Y4">
+        <v>0.262369634</v>
+      </c>
+      <c r="Z4">
+        <v>0.362098635802615</v>
+      </c>
+      <c r="AA4">
+        <v>6.407418</v>
+      </c>
+      <c r="AB4">
+        <v>0.05739035225918354</v>
+      </c>
+      <c r="AC4">
+        <v>46.96840987539281</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.64075159722</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>830.5908475693222</v>
       </c>
-      <c r="V5">
-        <v>7.226623223226898</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>47.15072266271488</v>
+      </c>
+      <c r="X5">
+        <v>0.249567824</v>
+      </c>
+      <c r="Y5">
+        <v>0.262351806</v>
+      </c>
+      <c r="Z5">
+        <v>0.3620946960224032</v>
+      </c>
+      <c r="AA5">
+        <v>6.391990999999997</v>
+      </c>
+      <c r="AB5">
+        <v>0.05752405578385551</v>
+      </c>
+      <c r="AC5">
+        <v>47.77895424913753</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.64086733796</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>811.9085410216121</v>
       </c>
-      <c r="V6">
-        <v>9.484684837440961</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.249588476</v>
+      </c>
+      <c r="Y6">
+        <v>0.262337164</v>
+      </c>
+      <c r="Z6">
+        <v>0.3620983222379875</v>
+      </c>
+      <c r="AA6">
+        <v>6.374344000000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.0576790618179459</v>
+      </c>
+      <c r="AC6">
+        <v>46.83012292810383</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.64098365741</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>813.8517538733028</v>
       </c>
-      <c r="V7">
-        <v>10.27133480366354</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.249596102</v>
+      </c>
+      <c r="Y7">
+        <v>0.262311378</v>
+      </c>
+      <c r="Z7">
+        <v>0.362084897726836</v>
+      </c>
+      <c r="AA7">
+        <v>6.357638000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.05782399571641322</v>
+      </c>
+      <c r="AC7">
+        <v>47.06016032976525</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.64109997685</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>813.3730137048223</v>
       </c>
-      <c r="V8">
-        <v>1.012418603784612</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.249596738</v>
+      </c>
+      <c r="Y8">
+        <v>0.262289096</v>
+      </c>
+      <c r="Z8">
+        <v>0.3620691943548054</v>
+      </c>
+      <c r="AA8">
+        <v>6.346178999999999</v>
+      </c>
+      <c r="AB8">
+        <v>0.05792284856536385</v>
+      </c>
+      <c r="AC8">
+        <v>47.11288189997803</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.6412162963</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>818.7929543958337</v>
       </c>
-      <c r="V9">
-        <v>3.000566942174937</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.249584982</v>
+      </c>
+      <c r="Y9">
+        <v>0.262274452</v>
+      </c>
+      <c r="Z9">
+        <v>0.3620504818555565</v>
+      </c>
+      <c r="AA9">
+        <v>6.344735</v>
+      </c>
+      <c r="AB9">
+        <v>0.0579327333386119</v>
+      </c>
+      <c r="AC9">
+        <v>47.43491388654805</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.64133203703</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>802.0389760522668</v>
       </c>
-      <c r="V10">
-        <v>8.549190575139345</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.249580534</v>
+      </c>
+      <c r="Y10">
+        <v>0.262256944</v>
+      </c>
+      <c r="Z10">
+        <v>0.362034732626504</v>
+      </c>
+      <c r="AA10">
+        <v>6.338205000000002</v>
+      </c>
+      <c r="AB10">
+        <v>0.05798819405528481</v>
+      </c>
+      <c r="AC10">
+        <v>46.50879178322077</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.64144835648</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>813.8404690983767</v>
       </c>
-      <c r="V11">
-        <v>8.607149538567644</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.249556386</v>
+      </c>
+      <c r="Y11">
+        <v>0.262240392</v>
+      </c>
+      <c r="Z11">
+        <v>0.3620060952383187</v>
+      </c>
+      <c r="AA11">
+        <v>6.342002999999998</v>
+      </c>
+      <c r="AB11">
+        <v>0.05795005224611408</v>
+      </c>
+      <c r="AC11">
+        <v>47.16209770425292</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.64156409722</v>
       </c>
@@ -1269,11 +1470,26 @@
       <c r="U12">
         <v>822.6457069623131</v>
       </c>
-      <c r="V12">
-        <v>10.33960678456802</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.249513812</v>
+      </c>
+      <c r="Y12">
+        <v>0.262223202</v>
+      </c>
+      <c r="Z12">
+        <v>0.3619642938825653</v>
+      </c>
+      <c r="AA12">
+        <v>6.354695</v>
+      </c>
+      <c r="AB12">
+        <v>0.05783128164715671</v>
+      </c>
+      <c r="AC12">
+        <v>47.57465557516187</v>
       </c>
     </row>
   </sheetData>
